--- a/static/manifest_template.xlsx
+++ b/static/manifest_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\alner\Documents\GitHub\Docx_UTM_gen_web\static\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E01CBDAF-D649-4CCF-A0ED-0F4BAE7DEB77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBD572FE-B7AE-4208-A5B5-EDB4E8B028B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0D107AF1-B7F6-44A1-AB71-EA0DDCFE16B8}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>Имя файла статьи</t>
   </si>
@@ -79,6 +79,39 @@
   </si>
   <si>
     <t>Источники трафика (UTM source) через запятую</t>
+  </si>
+  <si>
+    <t>Тип трафика (UTM medium)</t>
+  </si>
+  <si>
+    <t>Идентификатор объявления (UTM content), необязательно</t>
+  </si>
+  <si>
+    <t>Ключевое слово (UTM term), необязательно</t>
+  </si>
+  <si>
+    <t>article</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>cpc</t>
+  </si>
+  <si>
+    <t>banner</t>
+  </si>
+  <si>
+    <t>link</t>
+  </si>
+  <si>
+    <t>landing page</t>
+  </si>
+  <si>
+    <t>free</t>
+  </si>
+  <si>
+    <t>discount</t>
   </si>
 </sst>
 </file>
@@ -124,9 +157,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -441,26 +477,38 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{708BB45B-05BB-4AF1-8963-38A2E2C49FEE}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" customWidth="1"/>
     <col min="2" max="2" width="26.28515625" customWidth="1"/>
     <col min="3" max="3" width="31.5703125" customWidth="1"/>
+    <col min="4" max="4" width="27.140625" customWidth="1"/>
+    <col min="5" max="5" width="30.5703125" customWidth="1"/>
+    <col min="6" max="6" width="25.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="D1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -470,8 +518,17 @@
       <c r="C2" t="s">
         <v>10</v>
       </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -481,8 +538,14 @@
       <c r="C3" t="s">
         <v>11</v>
       </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -492,8 +555,14 @@
       <c r="C4" t="s">
         <v>13</v>
       </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -502,6 +571,9 @@
       </c>
       <c r="C5" t="s">
         <v>12</v>
+      </c>
+      <c r="D5" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/static/manifest_template.xlsx
+++ b/static/manifest_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\alner\Documents\GitHub\Docx_UTM_gen_web\static\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBD572FE-B7AE-4208-A5B5-EDB4E8B028B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01D0FE4B-9E6D-46D0-8297-E3E174EDDF2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0D107AF1-B7F6-44A1-AB71-EA0DDCFE16B8}"/>
   </bookViews>
@@ -93,9 +93,6 @@
     <t>article</t>
   </si>
   <si>
-    <t>email</t>
-  </si>
-  <si>
     <t>cpc</t>
   </si>
   <si>
@@ -112,6 +109,9 @@
   </si>
   <si>
     <t>discount</t>
+  </si>
+  <si>
+    <t>messenger</t>
   </si>
 </sst>
 </file>
@@ -522,10 +522,10 @@
         <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -539,10 +539,10 @@
         <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -556,10 +556,10 @@
         <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -573,7 +573,7 @@
         <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
